--- a/site/Entra-ID-to-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-to-ServiceNow-Integration-Guide/headings.xlsx
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">

--- a/site/Entra-ID-to-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-to-ServiceNow-Integration-Guide/headings.xlsx
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Onboarding Ticket Settings</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Offboarding Ticket Settings</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">

--- a/site/Entra-ID-to-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-to-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Group Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,54 +957,76 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-to-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-to-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,29 +705,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>User Provisioning Threshold Settings</t>
+          <t>Obtaining Application ID</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01KF2STBQHQZSSRVHSD95EW224</t>
+          <t>h_01EZ6MJ9GSXNHBXTBEC4JTG3FM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KF2STBQHQZSSRVHSD95EW224</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01EZ6MJ9GSXNHBXTBEC4JTG3FM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Create User Settings</t>
+          <t>User Provisioning Threshold Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+          <t>01KF2STBQHQZSSRVHSD95EW224</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KF2STBQHQZSSRVHSD95EW224</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Update User Settings</t>
+          <t>Create User Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWGD83B6WJD2G64H6F</t>
+          <t>h_01KGPAMEAW55WS81E8WGSSTNW2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAWGD83B6WJD2G64H6F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAW55WS81E8WGSSTNW2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Group Management</t>
+          <t>Update User Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
+          <t>h_01KGPAMEAWGD83B6WJD2G64H6F</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAWGD83B6WJD2G64H6F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Group Management</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,54 +979,76 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-to-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
